--- a/data/final/repr_bootstrap.xlsx
+++ b/data/final/repr_bootstrap.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6669251</v>
+        <v>0.6668282999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0.667</v>
@@ -524,7 +524,7 @@
         <v>0.696</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01479209148792214</v>
+        <v>0.01488551567691548</v>
       </c>
       <c r="H3" t="n">
         <v>10000</v>
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6159281</v>
+        <v>0.6163351999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0.616</v>
       </c>
       <c r="E4" t="n">
-        <v>0.585</v>
+        <v>0.586</v>
       </c>
       <c r="F4" t="n">
         <v>0.646</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01548489291473656</v>
+        <v>0.01532590386544721</v>
       </c>
       <c r="H4" t="n">
         <v>10000</v>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04120836702057072</v>
+        <v>0.04111326562707372</v>
       </c>
       <c r="D5" t="n">
         <v>0.0412534837425349</v>
@@ -584,7 +584,7 @@
         <v>0.07025348374253482</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01470890790392239</v>
+        <v>0.01479833311972654</v>
       </c>
       <c r="H5" t="n">
         <v>10000</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01468278214996682</v>
+        <v>0.01442323092236231</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01274651625746515</v>
+        <v>0.01225348374253488</v>
       </c>
       <c r="E6" t="n">
         <v>0.0007465162574651352</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04074651625746517</v>
+        <v>0.03974651625746517</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01098122011668089</v>
+        <v>0.01074312179419131</v>
       </c>
       <c r="H6" t="n">
         <v>10000</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06585472863202553</v>
+        <v>0.06570274793213159</v>
       </c>
       <c r="D7" t="n">
         <v>0.06592682926829278</v>
@@ -644,7 +644,7 @@
         <v>0.112271474019088</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02350617625791203</v>
+        <v>0.02364908590819502</v>
       </c>
       <c r="H7" t="n">
         <v>10000</v>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0234644249204666</v>
+        <v>0.02304963838812301</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02037009544008481</v>
+        <v>0.01958218451749741</v>
       </c>
       <c r="E8" t="n">
         <v>0.001193001060445343</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06511664899257689</v>
+        <v>0.06351855779427361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01754899121509873</v>
+        <v>0.01716848838159735</v>
       </c>
       <c r="H8" t="n">
         <v>10000</v>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.585472863202554</v>
+        <v>6.570274793213158</v>
       </c>
       <c r="D9" t="n">
         <v>6.592682926829278</v>
@@ -704,7 +704,7 @@
         <v>11.2271474019088</v>
       </c>
       <c r="G9" t="n">
-        <v>2.350617625791203</v>
+        <v>2.364908590819502</v>
       </c>
       <c r="H9" t="n">
         <v>10000</v>
@@ -722,19 +722,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.34644249204666</v>
+        <v>2.304963838812301</v>
       </c>
       <c r="D10" t="n">
-        <v>2.037009544008481</v>
+        <v>1.958218451749741</v>
       </c>
       <c r="E10" t="n">
         <v>0.1193001060445343</v>
       </c>
       <c r="F10" t="n">
-        <v>6.511664899257689</v>
+        <v>6.35185577942736</v>
       </c>
       <c r="G10" t="n">
-        <v>1.754899121509873</v>
+        <v>1.716848838159735</v>
       </c>
       <c r="H10" t="n">
         <v>10000</v>
@@ -748,11 +748,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9341452713679744</v>
+        <v>0.9342972520678684</v>
       </c>
       <c r="D11" t="n">
         <v>0.9340731707317073</v>
@@ -764,7 +764,7 @@
         <v>0.9804178154825026</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02350617625791203</v>
+        <v>0.02364908590819502</v>
       </c>
       <c r="H11" t="n">
         <v>10000</v>
@@ -778,23 +778,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9765355750795334</v>
+        <v>0.9769503616118769</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9796299045599152</v>
+        <v>0.9804178154825026</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9348833510074231</v>
+        <v>0.9364814422057264</v>
       </c>
       <c r="F12" t="n">
         <v>0.9988069989395546</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01754899121509872</v>
+        <v>0.01716848838159734</v>
       </c>
       <c r="H12" t="n">
         <v>10000</v>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.2042369</v>
+        <v>38.2080608</v>
       </c>
       <c r="D14" t="n">
-        <v>38.2</v>
+        <v>38.20950000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>37.592975</v>
+        <v>37.585</v>
       </c>
       <c r="F14" t="n">
-        <v>38.835</v>
+        <v>38.834</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3150079703444471</v>
+        <v>0.3169435773548387</v>
       </c>
       <c r="H14" t="n">
         <v>10000</v>
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39.1994552140211</v>
+        <v>39.19902975165142</v>
       </c>
       <c r="D15" t="n">
-        <v>39.198</v>
+        <v>39.1992989983972</v>
       </c>
       <c r="E15" t="n">
-        <v>38.55996396396397</v>
+        <v>38.54108011022044</v>
       </c>
       <c r="F15" t="n">
-        <v>39.86102154654655</v>
+        <v>39.86288447766403</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3307669276375857</v>
+        <v>0.3373482355480265</v>
       </c>
       <c r="H15" t="n">
         <v>10000</v>
@@ -902,19 +902,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6676660573846674</v>
+        <v>0.6636189218718896</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6672419515433106</v>
+        <v>0.6577419515433114</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0837451460338529</v>
+        <v>0.08074514603385279</v>
       </c>
       <c r="F16" t="n">
-        <v>1.27426695154331</v>
+        <v>1.282241951543313</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3050035004393943</v>
+        <v>0.3075424543425541</v>
       </c>
       <c r="H16" t="n">
         <v>10000</v>
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3849467222823488</v>
+        <v>0.3898469247637776</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3439692596679009</v>
+        <v>0.3489742646729042</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01564093133956845</v>
+        <v>0.01924195154331443</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9946415000445461</v>
+        <v>0.9964889135903584</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2675530806738603</v>
+        <v>0.2681457838809136</v>
       </c>
       <c r="H17" t="n">
         <v>10000</v>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01717811771200699</v>
+        <v>0.01707399055223004</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0171672060594157</v>
+        <v>0.01692278429128914</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002154645964801411</v>
+        <v>0.002077460143287749</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03278511382752518</v>
+        <v>0.03299029946971573</v>
       </c>
       <c r="G18" t="n">
-        <v>0.007847315248652044</v>
+        <v>0.007912638996252278</v>
       </c>
       <c r="H18" t="n">
         <v>10000</v>
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.009904142999451072</v>
+        <v>0.01003021838415519</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008849849960970612</v>
+        <v>0.008978621768634327</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0004024193782277724</v>
+        <v>0.0004950686124655774</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02559074043083861</v>
+        <v>0.02563827180824161</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006883768110107347</v>
+        <v>0.006899017538090744</v>
       </c>
       <c r="H19" t="n">
         <v>10000</v>
@@ -1022,19 +1022,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.717811771200699</v>
+        <v>1.707399055223004</v>
       </c>
       <c r="D20" t="n">
-        <v>1.71672060594157</v>
+        <v>1.692278429128914</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2154645964801411</v>
+        <v>0.2077460143287749</v>
       </c>
       <c r="F20" t="n">
-        <v>3.278511382752519</v>
+        <v>3.299029946971573</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7847315248652043</v>
+        <v>0.7912638996252278</v>
       </c>
       <c r="H20" t="n">
         <v>10000</v>
@@ -1052,19 +1052,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9904142999451073</v>
+        <v>1.003021838415519</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8849849960970612</v>
+        <v>0.8978621768634327</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04024193782277725</v>
+        <v>0.04950686124655774</v>
       </c>
       <c r="F21" t="n">
-        <v>2.559074043083861</v>
+        <v>2.563827180824161</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6883768110107347</v>
+        <v>0.6899017538090745</v>
       </c>
       <c r="H21" t="n">
         <v>10000</v>
@@ -1078,23 +1078,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9828218822879929</v>
+        <v>0.9829260094477701</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9828327939405843</v>
+        <v>0.9830772157087109</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9672148861724749</v>
+        <v>0.9670097005302842</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9978453540351986</v>
+        <v>0.9979225398567122</v>
       </c>
       <c r="G22" t="n">
-        <v>0.007847315248652044</v>
+        <v>0.007912638996252278</v>
       </c>
       <c r="H22" t="n">
         <v>10000</v>
@@ -1108,23 +1108,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.990095857000549</v>
+        <v>0.9899697816158448</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9911501500390294</v>
+        <v>0.9910213782313657</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9744092595691614</v>
+        <v>0.9743617281917584</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9995975806217722</v>
+        <v>0.9995049313875344</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006883768110107346</v>
+        <v>0.006899017538090744</v>
       </c>
       <c r="H23" t="n">
         <v>10000</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1519922</v>
+        <v>0.1520853</v>
       </c>
       <c r="D25" t="n">
         <v>0.152</v>
@@ -1184,7 +1184,7 @@
         <v>0.175</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01150047674040192</v>
+        <v>0.01128910839290822</v>
       </c>
       <c r="H25" t="n">
         <v>10000</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1719176</v>
+        <v>0.1721087</v>
       </c>
       <c r="D26" t="n">
         <v>0.172</v>
@@ -1214,7 +1214,7 @@
         <v>0.196</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01191915336178229</v>
+        <v>0.01199496028410356</v>
       </c>
       <c r="H26" t="n">
         <v>10000</v>
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.009968929927007304</v>
+        <v>0.009769255806237564</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008602521566025229</v>
+        <v>0.008397478433974787</v>
       </c>
       <c r="E27" t="n">
         <v>0.0003974784339747794</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02760252156602522</v>
+        <v>0.02660252156602522</v>
       </c>
       <c r="G27" t="n">
-        <v>0.007357217753871582</v>
+        <v>0.007239018988678569</v>
       </c>
       <c r="H27" t="n">
         <v>10000</v>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01638148307896483</v>
+        <v>0.01656485248838752</v>
       </c>
       <c r="D28" t="n">
         <v>0.01539747843397477</v>
@@ -1274,7 +1274,7 @@
         <v>0.03939747843397479</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01040487750816819</v>
+        <v>0.01048441263328818</v>
       </c>
       <c r="H28" t="n">
         <v>10000</v>
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.06365753135593222</v>
+        <v>0.06238249364406782</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05493220338983059</v>
+        <v>0.05362288135593222</v>
       </c>
       <c r="E29" t="n">
         <v>0.002538135593220307</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1762584745762712</v>
+        <v>0.1698728813559322</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04698019980967997</v>
+        <v>0.04622543057601103</v>
       </c>
       <c r="H29" t="n">
         <v>10000</v>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1046054872881356</v>
+        <v>0.1057764097457627</v>
       </c>
       <c r="D30" t="n">
         <v>0.09832203389830496</v>
@@ -1334,7 +1334,7 @@
         <v>0.2515762711864407</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06644131527461639</v>
+        <v>0.06694919423036137</v>
       </c>
       <c r="H30" t="n">
         <v>10000</v>
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.365753135593223</v>
+        <v>6.238249364406783</v>
       </c>
       <c r="D31" t="n">
-        <v>5.493220338983059</v>
+        <v>5.362288135593221</v>
       </c>
       <c r="E31" t="n">
         <v>0.2538135593220308</v>
       </c>
       <c r="F31" t="n">
-        <v>17.62584745762712</v>
+        <v>16.98728813559322</v>
       </c>
       <c r="G31" t="n">
-        <v>4.698019980967997</v>
+        <v>4.622543057601103</v>
       </c>
       <c r="H31" t="n">
         <v>10000</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10.46054872881355</v>
+        <v>10.57764097457627</v>
       </c>
       <c r="D32" t="n">
         <v>9.832203389830497</v>
@@ -1394,7 +1394,7 @@
         <v>25.15762711864406</v>
       </c>
       <c r="G32" t="n">
-        <v>6.644131527461639</v>
+        <v>6.694919423036136</v>
       </c>
       <c r="H32" t="n">
         <v>10000</v>
@@ -1408,23 +1408,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9363424686440678</v>
+        <v>0.9376175063559322</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9450677966101694</v>
+        <v>0.9463771186440678</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8237415254237288</v>
+        <v>0.8301271186440677</v>
       </c>
       <c r="F33" t="n">
         <v>0.9974618644067796</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04698019980967998</v>
+        <v>0.04622543057601103</v>
       </c>
       <c r="H33" t="n">
         <v>10000</v>
@@ -1438,11 +1438,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.8953945127118644</v>
+        <v>0.8942235902542374</v>
       </c>
       <c r="D34" t="n">
         <v>0.901677966101695</v>
@@ -1454,7 +1454,7 @@
         <v>0.9961525423728813</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0664413152746164</v>
+        <v>0.06694919423036137</v>
       </c>
       <c r="H34" t="n">
         <v>10000</v>
@@ -1502,19 +1502,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2899519.0593944</v>
+        <v>2898085.6253058</v>
       </c>
       <c r="D36" t="n">
-        <v>2899888.6565</v>
+        <v>2897332.681</v>
       </c>
       <c r="E36" t="n">
-        <v>2720185.08825</v>
+        <v>2720240.4348</v>
       </c>
       <c r="F36" t="n">
-        <v>3084258.076475</v>
+        <v>3081412.644475</v>
       </c>
       <c r="G36" t="n">
-        <v>92611.461620794</v>
+        <v>91796.94693387992</v>
       </c>
       <c r="H36" t="n">
         <v>10000</v>
@@ -1532,19 +1532,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2172643.7555839</v>
+        <v>2173105.9151329</v>
       </c>
       <c r="D37" t="n">
-        <v>2172689.434</v>
+        <v>2172491.1705</v>
       </c>
       <c r="E37" t="n">
-        <v>2028157.067925</v>
+        <v>2027142.9985</v>
       </c>
       <c r="F37" t="n">
-        <v>2319299.49315</v>
+        <v>2330312.874225</v>
       </c>
       <c r="G37" t="n">
-        <v>75531.93020084548</v>
+        <v>76658.13864852587</v>
       </c>
       <c r="H37" t="n">
         <v>10000</v>
@@ -1562,19 +1562,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>250316.2227647665</v>
+        <v>248909.2572474509</v>
       </c>
       <c r="D38" t="n">
-        <v>250550.2918682816</v>
+        <v>247994.3163682816</v>
       </c>
       <c r="E38" t="n">
-        <v>71858.75764328166</v>
+        <v>70980.34284328175</v>
       </c>
       <c r="F38" t="n">
-        <v>434919.7118432816</v>
+        <v>432074.2798432813</v>
       </c>
       <c r="G38" t="n">
-        <v>92244.48326292758</v>
+        <v>91356.73348523377</v>
       </c>
       <c r="H38" t="n">
         <v>10000</v>
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>476694.6090478186</v>
+        <v>476232.4494988185</v>
       </c>
       <c r="D39" t="n">
-        <v>476648.9306317186</v>
+        <v>476847.1941317185</v>
       </c>
       <c r="E39" t="n">
-        <v>330038.8714817184</v>
+        <v>319025.4904067186</v>
       </c>
       <c r="F39" t="n">
-        <v>621181.2967067185</v>
+        <v>622195.3661317185</v>
       </c>
       <c r="G39" t="n">
-        <v>75531.93020084548</v>
+        <v>76658.13864852587</v>
       </c>
       <c r="H39" t="n">
         <v>10000</v>
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.09448254179475585</v>
+        <v>0.09395147881839223</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09457089181702552</v>
+        <v>0.09360613188521694</v>
       </c>
       <c r="E40" t="n">
-        <v>0.02712328428961193</v>
+        <v>0.02679172422475701</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1641616328247824</v>
+        <v>0.1630876167466603</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03481793208990517</v>
+        <v>0.03448284851222964</v>
       </c>
       <c r="H40" t="n">
         <v>10000</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.179929681844955</v>
+        <v>0.1797552384612145</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1799124404020688</v>
+        <v>0.1799872755015211</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1245740732432253</v>
+        <v>0.1204170424833847</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2344665766364155</v>
+        <v>0.2348493399098945</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02850973330141056</v>
+        <v>0.02893482375520653</v>
       </c>
       <c r="H41" t="n">
         <v>10000</v>
@@ -1682,19 +1682,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9.448254179475583</v>
+        <v>9.395147881839225</v>
       </c>
       <c r="D42" t="n">
-        <v>9.457089181702552</v>
+        <v>9.360613188521693</v>
       </c>
       <c r="E42" t="n">
-        <v>2.712328428961193</v>
+        <v>2.679172422475701</v>
       </c>
       <c r="F42" t="n">
-        <v>16.41616328247824</v>
+        <v>16.30876167466603</v>
       </c>
       <c r="G42" t="n">
-        <v>3.481793208990517</v>
+        <v>3.448284851222964</v>
       </c>
       <c r="H42" t="n">
         <v>10000</v>
@@ -1712,19 +1712,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17.9929681844955</v>
+        <v>17.97552384612144</v>
       </c>
       <c r="D43" t="n">
-        <v>17.99124404020689</v>
+        <v>17.99872755015211</v>
       </c>
       <c r="E43" t="n">
-        <v>12.45740732432253</v>
+        <v>12.04170424833847</v>
       </c>
       <c r="F43" t="n">
-        <v>23.44665766364155</v>
+        <v>23.48493399098945</v>
       </c>
       <c r="G43" t="n">
-        <v>2.850973330141055</v>
+        <v>2.893482375520653</v>
       </c>
       <c r="H43" t="n">
         <v>10000</v>
@@ -1738,23 +1738,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9055174582052441</v>
+        <v>0.9060485211816076</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9054291081829744</v>
+        <v>0.9063938681147831</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8358383671752175</v>
+        <v>0.8369123832533397</v>
       </c>
       <c r="F44" t="n">
-        <v>0.972876715710388</v>
+        <v>0.9732082757752429</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03481793208990517</v>
+        <v>0.03448284851222964</v>
       </c>
       <c r="H44" t="n">
         <v>10000</v>
@@ -1768,23 +1768,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.8200703181550448</v>
+        <v>0.8202447615387854</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8200875595979311</v>
+        <v>0.8200127244984788</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7655334233635845</v>
+        <v>0.7651506600901055</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8754259267567748</v>
+        <v>0.8795829575166153</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02850973330141056</v>
+        <v>0.02893482375520653</v>
       </c>
       <c r="H45" t="n">
         <v>10000</v>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.5541133</v>
+        <v>0.5543777</v>
       </c>
       <c r="D47" t="n">
         <v>0.554</v>
@@ -1844,7 +1844,7 @@
         <v>0.585</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0156832349818508</v>
+        <v>0.0159356279177732</v>
       </c>
       <c r="H47" t="n">
         <v>10000</v>
@@ -1862,19 +1862,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.5538021000000001</v>
+        <v>0.5539386000000002</v>
       </c>
       <c r="D48" t="n">
         <v>0.554</v>
       </c>
       <c r="E48" t="n">
-        <v>0.524</v>
+        <v>0.523</v>
       </c>
       <c r="F48" t="n">
         <v>0.585</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01557483846302472</v>
+        <v>0.01572008085647821</v>
       </c>
       <c r="H48" t="n">
         <v>10000</v>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0125766132050431</v>
+        <v>0.01281643988055737</v>
       </c>
       <c r="D49" t="n">
         <v>0.01092833443928332</v>
@@ -1901,10 +1901,10 @@
         <v>7.166556071658281e-05</v>
       </c>
       <c r="F49" t="n">
-        <v>0.03507166556071661</v>
+        <v>0.03592833443928334</v>
       </c>
       <c r="G49" t="n">
-        <v>0.009571437734852944</v>
+        <v>0.00961958858098404</v>
       </c>
       <c r="H49" t="n">
         <v>10000</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.01257053384207031</v>
+        <v>0.01262557518248172</v>
       </c>
       <c r="D50" t="n">
         <v>0.01092833443928332</v>
@@ -1931,10 +1931,10 @@
         <v>7.166556071658281e-05</v>
       </c>
       <c r="F50" t="n">
-        <v>0.03507166556071661</v>
+        <v>0.03592833443928334</v>
       </c>
       <c r="G50" t="n">
-        <v>0.009470634173112136</v>
+        <v>0.009604700675467337</v>
       </c>
       <c r="H50" t="n">
         <v>10000</v>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.02261689272076367</v>
+        <v>0.02304818007159899</v>
       </c>
       <c r="D51" t="n">
         <v>0.01965274463007155</v>
@@ -1961,10 +1961,10 @@
         <v>0.0001288782816227808</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06307040572792355</v>
+        <v>0.06461097852028638</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01721259745396585</v>
+        <v>0.0172991885340608</v>
       </c>
       <c r="H51" t="n">
         <v>10000</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.02260596002386629</v>
+        <v>0.02270494248210018</v>
       </c>
       <c r="D52" t="n">
         <v>0.01965274463007155</v>
@@ -1991,10 +1991,10 @@
         <v>0.0001288782816227808</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06307040572792355</v>
+        <v>0.06461097852028638</v>
       </c>
       <c r="G52" t="n">
-        <v>0.01703131944973746</v>
+        <v>0.01727241517652658</v>
       </c>
       <c r="H52" t="n">
         <v>10000</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.261689272076367</v>
+        <v>2.304818007159899</v>
       </c>
       <c r="D53" t="n">
         <v>1.965274463007155</v>
@@ -2021,10 +2021,10 @@
         <v>0.01288782816227808</v>
       </c>
       <c r="F53" t="n">
-        <v>6.307040572792355</v>
+        <v>6.461097852028638</v>
       </c>
       <c r="G53" t="n">
-        <v>1.721259745396585</v>
+        <v>1.72991885340608</v>
       </c>
       <c r="H53" t="n">
         <v>10000</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.260596002386629</v>
+        <v>2.270494248210018</v>
       </c>
       <c r="D54" t="n">
         <v>1.965274463007155</v>
@@ -2051,10 +2051,10 @@
         <v>0.01288782816227808</v>
       </c>
       <c r="F54" t="n">
-        <v>6.307040572792355</v>
+        <v>6.461097852028638</v>
       </c>
       <c r="G54" t="n">
-        <v>1.703131944973746</v>
+        <v>1.727241517652659</v>
       </c>
       <c r="H54" t="n">
         <v>10000</v>
@@ -2068,23 +2068,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.9773831072792362</v>
+        <v>0.9769518199284009</v>
       </c>
       <c r="D55" t="n">
         <v>0.9803472553699284</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9369295942720764</v>
+        <v>0.9353890214797136</v>
       </c>
       <c r="F55" t="n">
         <v>0.9998711217183772</v>
       </c>
       <c r="G55" t="n">
-        <v>0.01721259745396585</v>
+        <v>0.0172991885340608</v>
       </c>
       <c r="H55" t="n">
         <v>10000</v>
@@ -2098,23 +2098,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.9773940399761337</v>
+        <v>0.9772950575178997</v>
       </c>
       <c r="D56" t="n">
         <v>0.9803472553699284</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9369295942720764</v>
+        <v>0.9353890214797136</v>
       </c>
       <c r="F56" t="n">
         <v>0.9998711217183772</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01703131944973746</v>
+        <v>0.01727241517652658</v>
       </c>
       <c r="H56" t="n">
         <v>10000</v>
@@ -2162,19 +2162,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.491813391666667</v>
+        <v>2.492966296666667</v>
       </c>
       <c r="D58" t="n">
-        <v>2.488208333333333</v>
+        <v>2.488183333333333</v>
       </c>
       <c r="E58" t="n">
-        <v>2.325682916666667</v>
+        <v>2.322933333333333</v>
       </c>
       <c r="F58" t="n">
-        <v>2.680704166666667</v>
+        <v>2.690385</v>
       </c>
       <c r="G58" t="n">
-        <v>0.09092717290985952</v>
+        <v>0.09341498496835558</v>
       </c>
       <c r="H58" t="n">
         <v>10000</v>
@@ -2192,19 +2192,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2.390077608333333</v>
+        <v>2.389554116666667</v>
       </c>
       <c r="D59" t="n">
-        <v>2.38615</v>
+        <v>2.386566666666667</v>
       </c>
       <c r="E59" t="n">
-        <v>2.228347083333333</v>
+        <v>2.228899166666666</v>
       </c>
       <c r="F59" t="n">
-        <v>2.568792083333333</v>
+        <v>2.569304166666667</v>
       </c>
       <c r="G59" t="n">
-        <v>0.08700812673791899</v>
+        <v>0.08626688114075676</v>
       </c>
       <c r="H59" t="n">
         <v>10000</v>
@@ -2222,19 +2222,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.08239364965785924</v>
+        <v>0.08425381026703661</v>
       </c>
       <c r="D60" t="n">
-        <v>0.06786087902917703</v>
+        <v>0.06935833333333319</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003314120970823164</v>
+        <v>0.003230498255615258</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2404400456958433</v>
+        <v>0.2501933790291765</v>
       </c>
       <c r="G60" t="n">
-        <v>0.06431136290558097</v>
+        <v>0.0663682306036671</v>
       </c>
       <c r="H60" t="n">
         <v>10000</v>
@@ -2252,19 +2252,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.08201134073364708</v>
+        <v>0.08157577629929023</v>
       </c>
       <c r="D61" t="n">
-        <v>0.07224166666666698</v>
+        <v>0.07159999999999989</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003712870970823145</v>
+        <v>0.003413831588948471</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2157320376374896</v>
+        <v>0.21423578763749</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05798982152716604</v>
+        <v>0.05795225352253213</v>
       </c>
       <c r="H61" t="n">
         <v>10000</v>
@@ -2282,19 +2282,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.03376423435061617</v>
+        <v>0.03452651274220164</v>
       </c>
       <c r="D62" t="n">
-        <v>0.02780882546524496</v>
+        <v>0.02842246982090611</v>
       </c>
       <c r="E62" t="n">
-        <v>0.001358099290295138</v>
+        <v>0.001323831395074584</v>
       </c>
       <c r="F62" t="n">
-        <v>0.09853033679001427</v>
+        <v>0.1025271719069659</v>
       </c>
       <c r="G62" t="n">
-        <v>0.02635426319344303</v>
+        <v>0.02719715051879855</v>
       </c>
       <c r="H62" t="n">
         <v>10000</v>
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.03360756732390921</v>
+        <v>0.03342907663078557</v>
       </c>
       <c r="D63" t="n">
-        <v>0.02960403590982057</v>
+        <v>0.02934108623107358</v>
       </c>
       <c r="E63" t="n">
-        <v>0.001521503733516368</v>
+        <v>0.001398959874716483</v>
       </c>
       <c r="F63" t="n">
-        <v>0.08840519998780452</v>
+        <v>0.08779204914599958</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0237637479602395</v>
+        <v>0.02374835290348681</v>
       </c>
       <c r="H63" t="n">
         <v>10000</v>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3.376423435061618</v>
+        <v>3.452651274220164</v>
       </c>
       <c r="D64" t="n">
-        <v>2.780882546524496</v>
+        <v>2.842246982090611</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1358099290295139</v>
+        <v>0.1323831395074584</v>
       </c>
       <c r="F64" t="n">
-        <v>9.853033679001427</v>
+        <v>10.25271719069659</v>
       </c>
       <c r="G64" t="n">
-        <v>2.635426319344303</v>
+        <v>2.719715051879855</v>
       </c>
       <c r="H64" t="n">
         <v>10000</v>
@@ -2372,19 +2372,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3.360756732390922</v>
+        <v>3.342907663078557</v>
       </c>
       <c r="D65" t="n">
-        <v>2.960403590982057</v>
+        <v>2.934108623107358</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1521503733516368</v>
+        <v>0.1398959874716483</v>
       </c>
       <c r="F65" t="n">
-        <v>8.840519998780453</v>
+        <v>8.779204914599958</v>
       </c>
       <c r="G65" t="n">
-        <v>2.376374796023951</v>
+        <v>2.374835290348681</v>
       </c>
       <c r="H65" t="n">
         <v>10000</v>
@@ -2398,23 +2398,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.966235765649384</v>
+        <v>0.9654734872577985</v>
       </c>
       <c r="D66" t="n">
-        <v>0.972191174534755</v>
+        <v>0.9715775301790939</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9014696632099858</v>
+        <v>0.8974728280930341</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9986419007097048</v>
+        <v>0.9986761686049254</v>
       </c>
       <c r="G66" t="n">
-        <v>0.02635426319344303</v>
+        <v>0.02719715051879855</v>
       </c>
       <c r="H66" t="n">
         <v>10000</v>
@@ -2428,23 +2428,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.9663924326760909</v>
+        <v>0.9665709233692145</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9703959640901794</v>
+        <v>0.9706589137689264</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9115948000121955</v>
+        <v>0.9122079508540004</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9984784962664837</v>
+        <v>0.9986010401252835</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0237637479602395</v>
+        <v>0.02374835290348681</v>
       </c>
       <c r="H67" t="n">
         <v>10000</v>
@@ -2492,19 +2492,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.4940175999999999</v>
+        <v>0.4942098</v>
       </c>
       <c r="D69" t="n">
         <v>0.494</v>
       </c>
       <c r="E69" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="F69" t="n">
         <v>0.525</v>
       </c>
       <c r="G69" t="n">
-        <v>0.01589674686519509</v>
+        <v>0.01568437387715532</v>
       </c>
       <c r="H69" t="n">
         <v>10000</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.7050695999999999</v>
+        <v>0.7049666999999999</v>
       </c>
       <c r="D70" t="n">
         <v>0.705</v>
@@ -2534,7 +2534,7 @@
         <v>0.733</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0144210385366397</v>
+        <v>0.01434236945090128</v>
       </c>
       <c r="H70" t="n">
         <v>10000</v>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.1138125260783012</v>
+        <v>0.1136203260783012</v>
       </c>
       <c r="D71" t="n">
         <v>0.1138301260783012</v>
@@ -2561,10 +2561,10 @@
         <v>0.0828301260783012</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1448301260783012</v>
+        <v>0.1438301260783012</v>
       </c>
       <c r="G71" t="n">
-        <v>0.01589674686519509</v>
+        <v>0.01568437387715532</v>
       </c>
       <c r="H71" t="n">
         <v>10000</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.09723947392169875</v>
+        <v>0.09713657392169875</v>
       </c>
       <c r="D72" t="n">
         <v>0.09716987392169874</v>
@@ -2594,7 +2594,7 @@
         <v>0.1251698739216988</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0144210385366397</v>
+        <v>0.01434236945090128</v>
       </c>
       <c r="H72" t="n">
         <v>10000</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.1872439703056768</v>
+        <v>0.1869277635371178</v>
       </c>
       <c r="D73" t="n">
         <v>0.1872729257641921</v>
@@ -2621,10 +2621,10 @@
         <v>0.1362718340611353</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2382740174672488</v>
+        <v>0.2366288209606986</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0261532724081321</v>
+        <v>0.02580387711012343</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.1599780427947599</v>
+        <v>0.1598087520742358</v>
       </c>
       <c r="D74" t="n">
         <v>0.1598635371179039</v>
@@ -2654,7 +2654,7 @@
         <v>0.2059290393013101</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02372544222130571</v>
+        <v>0.02359601611627537</v>
       </c>
       <c r="H74" t="n">
         <v>10000</v>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>18.72439703056768</v>
+        <v>18.69277635371179</v>
       </c>
       <c r="D75" t="n">
         <v>18.72729257641921</v>
@@ -2681,10 +2681,10 @@
         <v>13.62718340611353</v>
       </c>
       <c r="F75" t="n">
-        <v>23.82740174672488</v>
+        <v>23.66288209606986</v>
       </c>
       <c r="G75" t="n">
-        <v>2.61532724081321</v>
+        <v>2.580387711012343</v>
       </c>
       <c r="H75" t="n">
         <v>10000</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15.99780427947599</v>
+        <v>15.98087520742358</v>
       </c>
       <c r="D76" t="n">
         <v>15.98635371179039</v>
@@ -2714,7 +2714,7 @@
         <v>20.59290393013101</v>
       </c>
       <c r="G76" t="n">
-        <v>2.37254422213057</v>
+        <v>2.359601611627537</v>
       </c>
       <c r="H76" t="n">
         <v>10000</v>
@@ -2728,23 +2728,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.8127560296943233</v>
+        <v>0.8130722364628821</v>
       </c>
       <c r="D77" t="n">
         <v>0.8127270742358079</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7617259825327511</v>
+        <v>0.7633711790393014</v>
       </c>
       <c r="F77" t="n">
         <v>0.8637281659388647</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0261532724081321</v>
+        <v>0.02580387711012343</v>
       </c>
       <c r="H77" t="n">
         <v>10000</v>
@@ -2758,11 +2758,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.8400219572052401</v>
+        <v>0.8401912479257641</v>
       </c>
       <c r="D78" t="n">
         <v>0.8401364628820961</v>
@@ -2774,7 +2774,7 @@
         <v>0.8862019650655021</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02372544222130571</v>
+        <v>0.02359601611627537</v>
       </c>
       <c r="H78" t="n">
         <v>10000</v>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.5879497</v>
+        <v>0.5880529999999999</v>
       </c>
       <c r="D80" t="n">
         <v>0.588</v>
@@ -2831,10 +2831,10 @@
         <v>0.5570000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>0.618</v>
+        <v>0.619</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01562896658034808</v>
+        <v>0.01555842528856137</v>
       </c>
       <c r="H80" t="n">
         <v>10000</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.5841364999999999</v>
+        <v>0.5838205999999999</v>
       </c>
       <c r="D81" t="n">
         <v>0.584</v>
@@ -2864,7 +2864,7 @@
         <v>0.614</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0157070474273139</v>
+        <v>0.01549041028898499</v>
       </c>
       <c r="H81" t="n">
         <v>10000</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.01260069216987393</v>
+        <v>0.01237900544127406</v>
       </c>
       <c r="D82" t="n">
-        <v>0.01058195089581959</v>
+        <v>0.01041804910418043</v>
       </c>
       <c r="E82" t="n">
-        <v>0.000418049104180418</v>
+        <v>0.0005819508958195829</v>
       </c>
       <c r="F82" t="n">
-        <v>0.03541804910418045</v>
+        <v>0.0355819508958195</v>
       </c>
       <c r="G82" t="n">
-        <v>0.009388066005057333</v>
+        <v>0.009547115840337411</v>
       </c>
       <c r="H82" t="n">
         <v>10000</v>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.01333729230258795</v>
+        <v>0.01317295434638356</v>
       </c>
       <c r="D83" t="n">
-        <v>0.01158195089581959</v>
+        <v>0.01058195089581959</v>
       </c>
       <c r="E83" t="n">
         <v>0.0005819508958195829</v>
@@ -2924,7 +2924,7 @@
         <v>0.0365819508958195</v>
       </c>
       <c r="G83" t="n">
-        <v>0.009923007802702553</v>
+        <v>0.009980241184173089</v>
       </c>
       <c r="H83" t="n">
         <v>10000</v>
@@ -2942,19 +2942,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.02137224884637031</v>
+        <v>0.02099624220596513</v>
       </c>
       <c r="D84" t="n">
-        <v>0.01794822734946553</v>
+        <v>0.01767023072594249</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0007090602138434325</v>
+        <v>0.0009870568373664731</v>
       </c>
       <c r="F84" t="n">
-        <v>0.06007315700619013</v>
+        <v>0.06035115362971299</v>
       </c>
       <c r="G84" t="n">
-        <v>0.01592325882906179</v>
+        <v>0.01619302596667246</v>
       </c>
       <c r="H84" t="n">
         <v>10000</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.02262160889139002</v>
+        <v>0.02234287248171079</v>
       </c>
       <c r="D85" t="n">
-        <v>0.01964434440067543</v>
+        <v>0.01794822734946553</v>
       </c>
       <c r="E85" t="n">
         <v>0.0009870568373664731</v>
@@ -2984,7 +2984,7 @@
         <v>0.06204727068092289</v>
       </c>
       <c r="G85" t="n">
-        <v>0.01683058273345273</v>
+        <v>0.0169276572476633</v>
       </c>
       <c r="H85" t="n">
         <v>10000</v>
@@ -3002,19 +3002,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2.137224884637031</v>
+        <v>2.099624220596513</v>
       </c>
       <c r="D86" t="n">
-        <v>1.794822734946553</v>
+        <v>1.767023072594249</v>
       </c>
       <c r="E86" t="n">
-        <v>0.07090602138434325</v>
+        <v>0.09870568373664731</v>
       </c>
       <c r="F86" t="n">
-        <v>6.007315700619014</v>
+        <v>6.035115362971299</v>
       </c>
       <c r="G86" t="n">
-        <v>1.592325882906179</v>
+        <v>1.619302596667246</v>
       </c>
       <c r="H86" t="n">
         <v>10000</v>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2.262160889139002</v>
+        <v>2.234287248171079</v>
       </c>
       <c r="D87" t="n">
-        <v>1.964434440067544</v>
+        <v>1.794822734946553</v>
       </c>
       <c r="E87" t="n">
         <v>0.09870568373664731</v>
@@ -3044,7 +3044,7 @@
         <v>6.204727068092289</v>
       </c>
       <c r="G87" t="n">
-        <v>1.683058273345273</v>
+        <v>1.69276572476633</v>
       </c>
       <c r="H87" t="n">
         <v>10000</v>
@@ -3058,23 +3058,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.9786277511536297</v>
+        <v>0.9790037577940349</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9820517726505344</v>
+        <v>0.9823297692740575</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9399268429938099</v>
+        <v>0.939648846370287</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9992909397861566</v>
+        <v>0.9990129431626336</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01592325882906179</v>
+        <v>0.01619302596667246</v>
       </c>
       <c r="H88" t="n">
         <v>10000</v>
@@ -3088,14 +3088,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.9773783911086099</v>
+        <v>0.9776571275182893</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9803556555993246</v>
+        <v>0.9820517726505344</v>
       </c>
       <c r="E89" t="n">
         <v>0.9379527293190771</v>
@@ -3104,7 +3104,7 @@
         <v>0.9990129431626336</v>
       </c>
       <c r="G89" t="n">
-        <v>0.01683058273345273</v>
+        <v>0.0169276572476633</v>
       </c>
       <c r="H89" t="n">
         <v>10000</v>
@@ -3152,19 +3152,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.4100612</v>
+        <v>0.4099403</v>
       </c>
       <c r="D91" t="n">
         <v>0.41</v>
       </c>
       <c r="E91" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="F91" t="n">
-        <v>0.441</v>
+        <v>0.4410249999999996</v>
       </c>
       <c r="G91" t="n">
-        <v>0.01563585311232664</v>
+        <v>0.01553847741376334</v>
       </c>
       <c r="H91" t="n">
         <v>10000</v>
@@ -3182,19 +3182,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.4148713</v>
+        <v>0.4151937</v>
       </c>
       <c r="D92" t="n">
         <v>0.415</v>
       </c>
       <c r="E92" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="F92" t="n">
         <v>0.445</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0156880383657351</v>
+        <v>0.01548386758292425</v>
       </c>
       <c r="H92" t="n">
         <v>10000</v>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.0125690817518248</v>
+        <v>0.01232939781021897</v>
       </c>
       <c r="D93" t="n">
-        <v>0.01075912408759122</v>
+        <v>0.01024087591240874</v>
       </c>
       <c r="E93" t="n">
         <v>0.0002408759124087334</v>
@@ -3224,7 +3224,7 @@
         <v>0.03524087591240876</v>
       </c>
       <c r="G93" t="n">
-        <v>0.009390306594750455</v>
+        <v>0.009529446107604261</v>
       </c>
       <c r="H93" t="n">
         <v>10000</v>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.01351909416058393</v>
+        <v>0.01337647810218977</v>
       </c>
       <c r="D94" t="n">
-        <v>0.01175912408759122</v>
+        <v>0.01124087591240874</v>
       </c>
       <c r="E94" t="n">
         <v>0.0007591240875912675</v>
@@ -3254,7 +3254,7 @@
         <v>0.03724087591240877</v>
       </c>
       <c r="G94" t="n">
-        <v>0.01003457986418964</v>
+        <v>0.0101098962439975</v>
       </c>
       <c r="H94" t="n">
         <v>10000</v>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.03074936071428568</v>
+        <v>0.03016299107142854</v>
       </c>
       <c r="D95" t="n">
-        <v>0.02632142857142852</v>
+        <v>0.02505357142857139</v>
       </c>
       <c r="E95" t="n">
         <v>0.0005892857142856514</v>
@@ -3284,7 +3284,7 @@
         <v>0.08621428571428573</v>
       </c>
       <c r="G95" t="n">
-        <v>0.02297271434787165</v>
+        <v>0.02331310922753185</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.03307349821428568</v>
+        <v>0.03272459821428569</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0287678571428571</v>
+        <v>0.02749999999999996</v>
       </c>
       <c r="E96" t="n">
         <v>0.001857142857142922</v>
@@ -3314,7 +3314,7 @@
         <v>0.09110714285714287</v>
       </c>
       <c r="G96" t="n">
-        <v>0.02454888288203537</v>
+        <v>0.02473313902549389</v>
       </c>
       <c r="H96" t="n">
         <v>10000</v>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3.074936071428568</v>
+        <v>3.016299107142854</v>
       </c>
       <c r="D97" t="n">
-        <v>2.632142857142852</v>
+        <v>2.505357142857139</v>
       </c>
       <c r="E97" t="n">
         <v>0.05892857142856514</v>
@@ -3344,7 +3344,7 @@
         <v>8.621428571428574</v>
       </c>
       <c r="G97" t="n">
-        <v>2.297271434787165</v>
+        <v>2.331310922753185</v>
       </c>
       <c r="H97" t="n">
         <v>10000</v>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3.307349821428568</v>
+        <v>3.272459821428568</v>
       </c>
       <c r="D98" t="n">
-        <v>2.87678571428571</v>
+        <v>2.749999999999996</v>
       </c>
       <c r="E98" t="n">
         <v>0.1857142857142922</v>
@@ -3374,7 +3374,7 @@
         <v>9.110714285714288</v>
       </c>
       <c r="G98" t="n">
-        <v>2.454888288203537</v>
+        <v>2.47331390254939</v>
       </c>
       <c r="H98" t="n">
         <v>10000</v>
@@ -3388,14 +3388,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>coef_representatividad_control</t>
+          <t>coef_representativeness_control</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.9692506392857143</v>
+        <v>0.9698370089285714</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9736785714285715</v>
+        <v>0.9749464285714287</v>
       </c>
       <c r="E99" t="n">
         <v>0.9137857142857143</v>
@@ -3404,7 +3404,7 @@
         <v>0.9994107142857144</v>
       </c>
       <c r="G99" t="n">
-        <v>0.02297271434787165</v>
+        <v>0.02331310922753185</v>
       </c>
       <c r="H99" t="n">
         <v>10000</v>
@@ -3418,14 +3418,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>coef_representatividad_treatment</t>
+          <t>coef_representativeness_treatment</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.9669265017857144</v>
+        <v>0.9672754017857144</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9712321428571429</v>
+        <v>0.9725</v>
       </c>
       <c r="E100" t="n">
         <v>0.9088928571428572</v>
@@ -3434,7 +3434,7 @@
         <v>0.9981428571428571</v>
       </c>
       <c r="G100" t="n">
-        <v>0.02454888288203538</v>
+        <v>0.0247331390254939</v>
       </c>
       <c r="H100" t="n">
         <v>10000</v>
